--- a/PA_final.xlsx
+++ b/PA_final.xlsx
@@ -597,52 +597,52 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15599825.32</v>
+        <v>27664671.1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>18473006.52</v>
+        <v>32004914.02</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23766730.95</v>
+        <v>42924228.21</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>28525520.81</v>
+        <v>47717843.57</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30479818.4</v>
+        <v>53333304</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>27966575.84</v>
+        <v>48705436.45</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26790668.99</v>
+        <v>47544140.97</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17471385.32</v>
+        <v>32502848.97</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22415640.83</v>
+        <v>40096918.19</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>22272011.37</v>
+        <v>37561363.61</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>22171026.19</v>
+        <v>36055670.75</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15669143.01</v>
+        <v>26884966.52</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>13960760.74</v>
+        <v>23261481</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>17998852.21</v>
+        <v>30182128.14</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>25111968.68</v>
+        <v>42909528.58</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>25659848.29</v>
+        <v>46669091.14</v>
       </c>
     </row>
     <row r="3">
@@ -652,52 +652,52 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14258361.16</v>
+        <v>15990492.71</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>17909646.53</v>
+        <v>19479839.05</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>23325640.23</v>
+        <v>25063317.97</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24827366.2</v>
+        <v>26675867.01</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>34522921.29</v>
+        <v>36284655.84</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>28894085.63</v>
+        <v>30815567</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>26971553.51</v>
+        <v>29064626.12</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20363595.47</v>
+        <v>21845899.81</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28842583.8</v>
+        <v>30525637.25</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>24421546.56</v>
+        <v>25824434.09</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>21665953.25</v>
+        <v>23209114.33</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>15057069.59</v>
+        <v>15994896.4</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>14589884.69</v>
+        <v>15401644.72</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>17314557.91</v>
+        <v>18266162.08</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>27410981.69</v>
+        <v>29380668.77</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>25863112.74</v>
+        <v>27878973.52</v>
       </c>
     </row>
     <row r="4">
@@ -707,52 +707,52 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>109511658.34</v>
+        <v>110365248.25</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>123049562.27</v>
+        <v>124432284.67</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>234051724.06</v>
+        <v>237227494.91</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>222452259.24</v>
+        <v>224956185.39</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>242323308.12</v>
+        <v>246173744.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>233368937.42</v>
+        <v>238486495.73</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>218744027.47</v>
+        <v>220979366.03</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>178878896.09</v>
+        <v>180657692.34</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>206966701.55</v>
+        <v>209157319.22</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>184037222.51</v>
+        <v>185602950.38</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>167295415.09</v>
+        <v>168899416.44</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>130513847.33</v>
+        <v>131960265.12</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>111178167.46</v>
+        <v>112309712.6</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>145748455.02</v>
+        <v>147220313.57</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>251229471.32</v>
+        <v>253580405.43</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>297687344.29</v>
+        <v>300098427.91</v>
       </c>
     </row>
     <row r="5">
@@ -762,52 +762,52 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>17005474.33</v>
+        <v>66069426.78</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>21820485.23</v>
+        <v>79157086.73999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33155671.11</v>
+        <v>120859885.3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39324291.56</v>
+        <v>143651172.52</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>41514374.89</v>
+        <v>152340177.39</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>44327098.33</v>
+        <v>155046386.37</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>53642151.13</v>
+        <v>165035649.51</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>95157410.14</v>
+        <v>182922833.02</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57850090.47</v>
+        <v>172228482.2</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>41218034.46</v>
+        <v>134244907.29</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>42100548.32</v>
+        <v>120410598.44</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35016582.53</v>
+        <v>104058891.2</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>27719164.62</v>
+        <v>80409422.94</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>40751557.31</v>
+        <v>101069188.25</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>62017646.55</v>
+        <v>156054702.46</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>65398934.15</v>
+        <v>164570416.01</v>
       </c>
     </row>
     <row r="6">
@@ -817,52 +817,52 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>165516509.03</v>
+        <v>172614179.51</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>175309413.24</v>
+        <v>181001131.24</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>316860470.45</v>
+        <v>329339492.45</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>344742208.69</v>
+        <v>356830976.19</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>370558084.26</v>
+        <v>382317210.76</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>350748457.45</v>
+        <v>361456395.95</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>339713246.3</v>
+        <v>350491575.8</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>282866148.2</v>
+        <v>291019375.2</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>325731472.35</v>
+        <v>335955987.1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>267830826.66</v>
+        <v>276413853.16</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>250870871.69</v>
+        <v>259597743.19</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>162161060.76</v>
+        <v>169032317.76</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>139500050.59</v>
+        <v>146444033.59</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>168915051.12</v>
+        <v>176936909.87</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>294444853.1</v>
+        <v>307199429.35</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>355123521.5</v>
+        <v>366232729</v>
       </c>
     </row>
     <row r="7">
@@ -872,52 +872,52 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>12522521.29</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>16960113.5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>19164705.57</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>20292305.34</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>21122679.21</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>17371840.07</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>18709163.69</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>13427458</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>15716652.6</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>15029604.51</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>15270222.84</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>12249865.27</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>10581244.78</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>12304470.84</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>17021697.94</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0</v>
+        <v>17532238.62</v>
       </c>
     </row>
     <row r="8">
@@ -927,52 +927,52 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>1171576.76</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>1681032.06</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>2887893.02</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>2425216.44</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>2603372.65</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>2434131.11</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>2431325.38</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1690020.01</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1955158.25</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1430423.63</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1639851.59</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>1238946.84</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>1213258.71</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>1615971.3</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0</v>
+        <v>2357657.47</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0</v>
+        <v>2157599.15</v>
       </c>
     </row>
   </sheetData>
@@ -1150,52 +1150,52 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1062513.13</v>
+        <v>2130699.12</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1221688.42</v>
+        <v>3113060.05</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1444657.73</v>
+        <v>3337121.78</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>777581.1800000001</v>
+        <v>1512642</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2126422.05</v>
+        <v>4476633.22</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>294468.8</v>
+        <v>56651.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1374722.54</v>
+        <v>2222184.03</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>154365.02</v>
+        <v>106598.13</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>915096.91</v>
+        <v>1795480.57</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>460659.68</v>
+        <v>1258912.73</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>951920.8199999999</v>
+        <v>2183782.01</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1155928.98</v>
+        <v>1891508.08</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1163414.73</v>
+        <v>2207624.73</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1772922.25</v>
+        <v>3162209.99</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>1213483.02</v>
+        <v>2640957.09</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1876258.53</v>
+        <v>3785549.27</v>
       </c>
     </row>
     <row r="3">
@@ -1205,52 +1205,52 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1027364.45</v>
+        <v>1461622.85</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-86321.46000000001</v>
+        <v>151949.26</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1558825.17</v>
+        <v>1916029.16</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>847978.51</v>
+        <v>961995.37</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1049119.99</v>
+        <v>1331124.94</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>154979.72</v>
+        <v>244342.99</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>524629.9399999999</v>
+        <v>478761.95</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-191998.1</v>
+        <v>-434061.96</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>499999.84</v>
+        <v>611976.4399999999</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1105911.18</v>
+        <v>1240685.66</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1006372.49</v>
+        <v>1115263.07</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>673633.98</v>
+        <v>904236.4399999999</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>979147.02</v>
+        <v>1067552</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>789254.28</v>
+        <v>973919.95</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>874616.75</v>
+        <v>1207476.18</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1518300.96</v>
+        <v>1824501.39</v>
       </c>
     </row>
     <row r="4">
@@ -1260,52 +1260,52 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10440565.04</v>
+        <v>10455311.54</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7526605.77</v>
+        <v>7773458.51</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12787538.68</v>
+        <v>13108980.73</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5929159.93</v>
+        <v>5854914.41</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20596165.62</v>
+        <v>21051942.75</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7197214.17</v>
+        <v>7289245.54</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14923156.04</v>
+        <v>14984228.51</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-186026.27</v>
+        <v>-153839.66</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8706610.439999999</v>
+        <v>8787240.800000001</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>12092299.31</v>
+        <v>12145574.98</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>15500610.71</v>
+        <v>15705766.08</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14047219.36</v>
+        <v>14186372.26</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>11193620.59</v>
+        <v>11272188.31</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>12094266</v>
+        <v>12274134.14</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>3870446.2</v>
+        <v>4097753.48</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>21666571</v>
+        <v>21773542.53</v>
       </c>
     </row>
     <row r="5">
@@ -1315,52 +1315,52 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>910252.21</v>
+        <v>4770718.71</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>395301.1</v>
+        <v>3793192.25</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>618293.78</v>
+        <v>5796312.369999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>351825.84</v>
+        <v>2075238.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1764332.33</v>
+        <v>9286792.279999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>824091.1</v>
+        <v>52289.6399999999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-1854442.1</v>
+        <v>2099876.34</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-423298.45</v>
+        <v>-4190319.57</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1130287.42</v>
+        <v>4571954.359999999</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1177446.05</v>
+        <v>4340163.87</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2653349.8</v>
+        <v>7615303.539999999</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2397583.81</v>
+        <v>7528942.040000001</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2518078.51</v>
+        <v>6449576.17</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3579929.03</v>
+        <v>9669216.49</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>231631.21</v>
+        <v>4019164.680000001</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>3502022.69</v>
+        <v>10457906.82</v>
       </c>
     </row>
     <row r="6">
@@ -1370,52 +1370,52 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17741157.22</v>
+        <v>18815150.08</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13128616.83</v>
+        <v>14078716.83</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>26601394.77</v>
+        <v>28789842.27</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>17370364.6</v>
+        <v>17934216.06</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>36751559.1</v>
+        <v>37848307.23</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13951976.04</v>
+        <v>14372664.11</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>28740201.89</v>
+        <v>29432359.18</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14203943.81</v>
+        <v>13096447.31</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9405311.49</v>
+        <v>9637468.58</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>20110269.78</v>
+        <v>20473948.53</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>28011011.79</v>
+        <v>29342505.74</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>22646443.3</v>
+        <v>23313596.55</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>15750321.56</v>
+        <v>16578578.03</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>18804947.18</v>
+        <v>19654872.47</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>15612752.35</v>
+        <v>17364908.04</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>18068538.45</v>
+        <v>19912547.67</v>
       </c>
     </row>
     <row r="7">
@@ -1425,52 +1425,52 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>985988.58</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>1242679.92</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2338796.53</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>893153.88</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>2128050.92</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>589238.8400000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1153417.2</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-762622</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>1139660.07</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>945821.8400000001</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>847973.71</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1067947.96</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>1226005.89</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1606269.22</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>1186471.67</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0</v>
+        <v>1571889.97</v>
       </c>
     </row>
     <row r="8">
@@ -1480,52 +1480,52 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>243081.69</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>131746.51</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>386392.86</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>215043.04</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>266238.22</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>104504.72</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>169891.59</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-88395.32000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>4402.52</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>207315.69</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>272585.64</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>137124.68</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>216870.95</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>222635.94</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0</v>
+        <v>245455.43</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0</v>
+        <v>284983.49</v>
       </c>
     </row>
   </sheetData>
@@ -1703,52 +1703,52 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.06811057868947983</v>
+        <v>0.07701877648565285</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.06613370805003105</v>
+        <v>0.09726818975531806</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.06078487331889454</v>
+        <v>0.07774447949707236</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.02725914051418156</v>
+        <v>0.03169971412855277</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.06976491861250722</v>
+        <v>0.08393691904030547</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0105293119073529</v>
+        <v>0.00116314654234045</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.05131348308297694</v>
+        <v>0.04673938753888059</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.008835305110196034</v>
+        <v>0.003279654964965984</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0408240351877551</v>
+        <v>0.04477851792729011</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.02068334432607646</v>
+        <v>0.03351616152893976</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.04293535228555877</v>
+        <v>0.06056695006845769</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.07377104027082333</v>
+        <v>0.07035560481702249</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.08333462278073536</v>
+        <v>0.09490473671904209</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.09850196164258632</v>
+        <v>0.1047709417749493</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.04832289477035139</v>
+        <v>0.06154710101455046</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.07312040620018803</v>
+        <v>0.08111469877662589</v>
       </c>
     </row>
     <row r="3">
@@ -1758,52 +1758,52 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.07205347364058493</v>
+        <v>0.09140574193101271</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-0.004819830467084042</v>
+        <v>0.007800334469395937</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.06682882676013904</v>
+        <v>0.07644754626236744</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.03415499264678346</v>
+        <v>0.03606238438808291</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.03038908501361068</v>
+        <v>0.03668561570129529</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.005363717751258011</v>
+        <v>0.007929206365081648</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.01945123182487385</v>
+        <v>0.01647232439954056</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.009428497059021573</v>
+        <v>-0.019869264428344</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.01733547325257316</v>
+        <v>0.02004794969513699</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.04528424018040567</v>
+        <v>0.04804309189026647</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.04644949051572425</v>
+        <v>0.04805280607189805</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.04473871731637524</v>
+        <v>0.05653281005308668</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.06711136111110691</v>
+        <v>0.06931415568973077</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.04558327646033442</v>
+        <v>0.05331825841326379</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.03190753107244879</v>
+        <v>0.04109764108681315</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.05870526781765868</v>
+        <v>0.0654436358171913</v>
       </c>
     </row>
     <row r="4">
@@ -1813,52 +1813,52 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.09533747546389314</v>
+        <v>0.09473372919269449</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.06116726976634697</v>
+        <v>0.06247139583280625</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.05463552439682891</v>
+        <v>0.05525911208130963</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.02665362873929335</v>
+        <v>0.02602691008406595</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.08499457101254433</v>
+        <v>0.08551660435364732</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.03084049766677812</v>
+        <v>0.0305646050007479</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.06822200456214357</v>
+        <v>0.0678082699719835</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.001039956496077681</v>
+        <v>-0.0008515533327552522</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.04206768709553316</v>
+        <v>0.042012590488202</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.06570572596716376</v>
+        <v>0.06543848012724679</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.09265412744073787</v>
+        <v>0.09298887119352087</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.1076301070527947</v>
+        <v>0.1075048784351821</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.1006818231108844</v>
+        <v>0.1003669945283076</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.08298040619600661</v>
+        <v>0.08337255805506706</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.01540601976218815</v>
+        <v>0.01615958249239084</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.07278297655439774</v>
+        <v>0.07255467041810003</v>
       </c>
     </row>
     <row r="5">
@@ -1868,52 +1868,52 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0535270109104919</v>
+        <v>0.07220766007075685</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.01811605451635504</v>
+        <v>0.04791980612499232</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.01864820585138203</v>
+        <v>0.04795894316474251</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.008946781392442713</v>
+        <v>0.01444637355613003</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.04249931101395418</v>
+        <v>0.06096088660987478</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.01859113569457954</v>
+        <v>0.0003372515878907155</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.03457061398424944</v>
+        <v>0.0127237742041471</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.004448402382717475</v>
+        <v>-0.02290758075861338</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.01953821352424931</v>
+        <v>0.02654586687172233</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.02856628331325821</v>
+        <v>0.03233019380485133</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.06302411502653797</v>
+        <v>0.06324446218739346</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.06846995442647498</v>
+        <v>0.07235270290867755</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.09084251075096071</v>
+        <v>0.08020920850050811</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.08784766193760951</v>
+        <v>0.09566928019727119</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.003734924217307308</v>
+        <v>0.02575484504243116</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05354862025683334</v>
+        <v>0.0635466997869443</v>
       </c>
     </row>
     <row r="6">
@@ -1923,52 +1923,52 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.1071866324632572</v>
+        <v>0.1090011848007538</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.07488825949138747</v>
+        <v>0.07778247977540098</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.08395302428296322</v>
+        <v>0.08741691455169424</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.05038653278345683</v>
+        <v>0.05025969508446111</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.09917894295409159</v>
+        <v>0.09899713160901699</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.03977772601320388</v>
+        <v>0.03976320317205885</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.08460135777166485</v>
+        <v>0.08397451240538489</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.05021436428638017</v>
+        <v>0.04500197727728474</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.02887443274100928</v>
+        <v>0.02868669989539829</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.07508571746869581</v>
+        <v>0.07406990748089899</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.111655098104068</v>
+        <v>0.1130306657501416</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.1396540155439472</v>
+        <v>0.1379239003460968</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.1129054899506184</v>
+        <v>0.1132076030930363</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.1113278364202173</v>
+        <v>0.1110840721952301</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.05302436835157571</v>
+        <v>0.05652649836212984</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.05087958796331096</v>
+        <v>0.05437129478943974</v>
       </c>
     </row>
     <row r="7">
@@ -1977,12 +1977,108 @@
           <t>Parx</t>
         </is>
       </c>
+      <c r="B7" s="3" t="n">
+        <v>0.07873722528923727</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.07327073135448062</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.122036653339517</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0440144116222923</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1007472063010136</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.03391919552710918</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.06164985346814291</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.05679570921018707</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.0725129007432537</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.06293058738642751</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.0555311941996519</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0.08718038414801275</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0.1158659416250646</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0.1305435431467933</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.06970348517417058</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.08965711704418955</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Unibet</t>
         </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.2074825127121846</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.0783723958245032</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.1337974978034332</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.08866962818378388</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.1022666578294122</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.04293306945162867</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.06987612246288484</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.0523043037815866</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.002251746118248996</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1449330713307637</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.166225798518755</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.1106784210370156</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.1787507876205562</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0.1377722116723236</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.10410987733515</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1320836124726875</v>
       </c>
     </row>
   </sheetData>
